--- a/docs/NCC - Prerequisites File.xlsx
+++ b/docs/NCC - Prerequisites File.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\issa.masadeh\Desktop\MES\System Integrators\IPIC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NEW WORKS\New folder\INDUSTRY360 MES PLATFORM\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8F8155E-0886-42DB-8FEF-C8D3DBD7FB08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54896229-4C9F-488A-9429-10EA50C2FE49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Site &amp; Hardware" sheetId="2" r:id="rId1"/>
@@ -594,13 +594,6 @@
     <t>Unplanned Downtime</t>
   </si>
   <si>
-    <t>M1 = Big Betti
-M2 = Cartomac
-M3 = Checkweigher
-M4 = Euro-Pack Robot
-M5 =  Uni-tech Wrapping</t>
-  </si>
-  <si>
     <t>Big Betti</t>
   </si>
   <si>
@@ -688,6 +681,13 @@
   </si>
   <si>
     <t>45 duplex / minute</t>
+  </si>
+  <si>
+    <t>M1 = Big Betti
+M2 = Checkweigher
+M3 = Cartomac
+M4 = Euro-Pack Robot
+M5 =  Uni-tech Wrapping</t>
   </si>
 </sst>
 </file>
@@ -1131,6 +1131,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1141,18 +1153,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="16" fontId="10" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1692,7 +1692,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -1702,8 +1702,8 @@
     <col min="6" max="6" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
+    <row r="1" spans="1:6" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="38"/>
@@ -1712,7 +1712,7 @@
       <c r="E1" s="38"/>
       <c r="F1" s="38"/>
     </row>
-    <row r="2" spans="1:6" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="37"/>
       <c r="B2" s="38"/>
       <c r="C2" s="38"/>
@@ -1720,7 +1720,7 @@
       <c r="E2" s="38"/>
       <c r="F2" s="38"/>
     </row>
-    <row r="3" spans="1:6" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
@@ -1740,7 +1740,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="46.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>8</v>
       </c>
@@ -1760,7 +1760,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="46.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>13</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="46.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>17</v>
       </c>
@@ -1800,7 +1800,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="46.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
         <v>21</v>
       </c>
@@ -1820,7 +1820,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="46.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>25</v>
       </c>
@@ -1840,7 +1840,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="46.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>29</v>
       </c>
@@ -1860,7 +1860,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="46.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>33</v>
       </c>
@@ -1892,7 +1892,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:CZ56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -1900,14 +1900,14 @@
     <col min="4" max="4" width="26" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="9" max="9" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="69.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="69.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="3.44140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="55" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:104" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="41" t="s">
+    <row r="1" spans="1:104" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="45" t="s">
         <v>38</v>
       </c>
       <c r="B1" s="38"/>
@@ -1916,7 +1916,7 @@
       <c r="E1" s="38"/>
       <c r="F1" s="38"/>
     </row>
-    <row r="2" spans="1:104" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:104" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="37"/>
       <c r="B2" s="38"/>
       <c r="C2" s="38"/>
@@ -1924,7 +1924,7 @@
       <c r="E2" s="38"/>
       <c r="F2" s="38"/>
     </row>
-    <row r="3" spans="1:104" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:104" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
         <v>2</v>
       </c>
@@ -1944,7 +1944,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:104" s="19" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:104" s="19" customFormat="1" ht="57" x14ac:dyDescent="0.3">
       <c r="A4" s="14">
         <v>1</v>
       </c>
@@ -2060,7 +2060,7 @@
       <c r="CY4" s="20"/>
       <c r="CZ4" s="26"/>
     </row>
-    <row r="5" spans="1:104" s="19" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:104" s="19" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="14">
         <v>2</v>
       </c>
@@ -2174,7 +2174,7 @@
       <c r="CY5" s="20"/>
       <c r="CZ5" s="26"/>
     </row>
-    <row r="6" spans="1:104" s="20" customFormat="1" ht="36" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:104" s="20" customFormat="1" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A6" s="14">
         <v>3</v>
       </c>
@@ -2194,7 +2194,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="7" spans="1:104" ht="46.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:104" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="14">
         <v>4</v>
       </c>
@@ -2214,7 +2214,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="8" spans="1:104" ht="46.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:104" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14">
         <v>5</v>
       </c>
@@ -2231,10 +2231,10 @@
         <v>12</v>
       </c>
       <c r="F8" s="33" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="9" spans="1:104" ht="46.15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="9" spans="1:104" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="14">
         <v>6</v>
       </c>
@@ -2254,7 +2254,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="10" spans="1:104" ht="46.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:104" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14">
         <v>7</v>
       </c>
@@ -2274,7 +2274,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="11" spans="1:104" ht="46.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:104" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="14">
         <v>8</v>
       </c>
@@ -2294,7 +2294,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="12" spans="1:104" ht="46.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:104" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14">
         <v>9</v>
       </c>
@@ -2312,29 +2312,29 @@
       </c>
       <c r="F12" s="25"/>
     </row>
-    <row r="13" spans="1:104" x14ac:dyDescent="0.25">
-      <c r="I13" s="42" t="s">
+    <row r="13" spans="1:104" x14ac:dyDescent="0.3">
+      <c r="I13" s="46" t="s">
         <v>98</v>
       </c>
-      <c r="J13" s="42"/>
-      <c r="L13" s="40" t="s">
+      <c r="J13" s="46"/>
+      <c r="L13" s="44" t="s">
         <v>172</v>
       </c>
-      <c r="M13" s="40"/>
-    </row>
-    <row r="14" spans="1:104" x14ac:dyDescent="0.25">
+      <c r="M13" s="44"/>
+    </row>
+    <row r="14" spans="1:104" x14ac:dyDescent="0.3">
       <c r="I14" s="27" t="s">
         <v>114</v>
       </c>
       <c r="J14" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="L14" s="40" t="s">
-        <v>174</v>
-      </c>
-      <c r="M14" s="40"/>
-    </row>
-    <row r="15" spans="1:104" x14ac:dyDescent="0.25">
+      <c r="L14" s="44" t="s">
+        <v>173</v>
+      </c>
+      <c r="M14" s="44"/>
+    </row>
+    <row r="15" spans="1:104" x14ac:dyDescent="0.3">
       <c r="I15" s="28">
         <v>10310064</v>
       </c>
@@ -2348,7 +2348,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="16" spans="1:104" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:104" x14ac:dyDescent="0.3">
       <c r="I16" s="28">
         <v>10310067</v>
       </c>
@@ -2362,7 +2362,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="17" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="9:13" x14ac:dyDescent="0.3">
       <c r="I17" s="28">
         <v>10310110</v>
       </c>
@@ -2376,7 +2376,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="18" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="9:13" x14ac:dyDescent="0.3">
       <c r="I18" s="28">
         <v>10310111</v>
       </c>
@@ -2390,7 +2390,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="19" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="9:13" x14ac:dyDescent="0.3">
       <c r="I19" s="28">
         <v>10310112</v>
       </c>
@@ -2404,7 +2404,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="20" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="9:13" x14ac:dyDescent="0.3">
       <c r="I20" s="28">
         <v>10310113</v>
       </c>
@@ -2418,7 +2418,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="21" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="9:13" x14ac:dyDescent="0.3">
       <c r="I21" s="28">
         <v>10310189</v>
       </c>
@@ -2432,7 +2432,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="22" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="9:13" x14ac:dyDescent="0.3">
       <c r="I22" s="28">
         <v>10310190</v>
       </c>
@@ -2446,7 +2446,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="23" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="9:13" x14ac:dyDescent="0.3">
       <c r="I23" s="28">
         <v>10310191</v>
       </c>
@@ -2460,7 +2460,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="24" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="9:13" x14ac:dyDescent="0.3">
       <c r="I24" s="28">
         <v>10310192</v>
       </c>
@@ -2474,7 +2474,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="25" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="9:13" x14ac:dyDescent="0.3">
       <c r="I25" s="28">
         <v>10310193</v>
       </c>
@@ -2488,7 +2488,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="26" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="9:13" x14ac:dyDescent="0.3">
       <c r="I26" s="28">
         <v>10310194</v>
       </c>
@@ -2502,7 +2502,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="27" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="9:13" x14ac:dyDescent="0.3">
       <c r="I27" s="28">
         <v>10310201</v>
       </c>
@@ -2516,7 +2516,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="28" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="9:13" x14ac:dyDescent="0.3">
       <c r="I28" s="28">
         <v>10310202</v>
       </c>
@@ -2530,7 +2530,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="29" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="9:13" x14ac:dyDescent="0.3">
       <c r="I29" s="28">
         <v>10310203</v>
       </c>
@@ -2544,7 +2544,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="30" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="9:13" x14ac:dyDescent="0.3">
       <c r="I30" s="28">
         <v>10310204</v>
       </c>
@@ -2558,7 +2558,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="31" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="9:13" x14ac:dyDescent="0.3">
       <c r="I31" s="28">
         <v>10310205</v>
       </c>
@@ -2572,7 +2572,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="32" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="9:13" x14ac:dyDescent="0.3">
       <c r="I32" s="28">
         <v>10310206</v>
       </c>
@@ -2586,19 +2586,19 @@
         <v>165</v>
       </c>
     </row>
-    <row r="33" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="9:13" x14ac:dyDescent="0.3">
       <c r="I33" s="28">
         <v>10310213</v>
       </c>
       <c r="J33" s="29" t="s">
         <v>134</v>
       </c>
-      <c r="L33" s="40" t="s">
-        <v>175</v>
-      </c>
-      <c r="M33" s="40"/>
-    </row>
-    <row r="34" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="L33" s="44" t="s">
+        <v>174</v>
+      </c>
+      <c r="M33" s="44"/>
+    </row>
+    <row r="34" spans="9:13" x14ac:dyDescent="0.3">
       <c r="I34" s="28">
         <v>10310214</v>
       </c>
@@ -2612,7 +2612,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="35" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="9:13" x14ac:dyDescent="0.3">
       <c r="I35" s="28">
         <v>10310215</v>
       </c>
@@ -2626,7 +2626,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="36" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="9:13" x14ac:dyDescent="0.3">
       <c r="I36" s="28">
         <v>10310216</v>
       </c>
@@ -2640,7 +2640,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="37" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="9:13" x14ac:dyDescent="0.3">
       <c r="I37" s="28">
         <v>10310217</v>
       </c>
@@ -2654,7 +2654,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="38" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="9:13" x14ac:dyDescent="0.3">
       <c r="I38" s="28">
         <v>10310218</v>
       </c>
@@ -2668,7 +2668,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="39" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="9:13" x14ac:dyDescent="0.3">
       <c r="I39" s="28">
         <v>10310219</v>
       </c>
@@ -2682,7 +2682,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="40" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="9:13" x14ac:dyDescent="0.3">
       <c r="I40" s="28">
         <v>10310220</v>
       </c>
@@ -2696,7 +2696,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="41" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="9:13" x14ac:dyDescent="0.3">
       <c r="I41" s="28">
         <v>10310235</v>
       </c>
@@ -2710,7 +2710,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="42" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="9:13" x14ac:dyDescent="0.3">
       <c r="I42" s="28">
         <v>10310236</v>
       </c>
@@ -2724,7 +2724,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="43" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="9:13" x14ac:dyDescent="0.3">
       <c r="I43" s="28">
         <v>10310290</v>
       </c>
@@ -2738,7 +2738,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="44" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="9:13" x14ac:dyDescent="0.3">
       <c r="I44" s="28">
         <v>10310291</v>
       </c>
@@ -2752,7 +2752,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="45" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="9:13" x14ac:dyDescent="0.3">
       <c r="I45" s="28">
         <v>10310297</v>
       </c>
@@ -2766,7 +2766,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="46" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="9:13" x14ac:dyDescent="0.3">
       <c r="I46" s="28">
         <v>10310298</v>
       </c>
@@ -2780,7 +2780,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="47" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="9:13" x14ac:dyDescent="0.3">
       <c r="L47" s="30">
         <v>14</v>
       </c>
@@ -2788,13 +2788,13 @@
         <v>164</v>
       </c>
     </row>
-    <row r="48" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="L48" s="40" t="s">
-        <v>176</v>
-      </c>
-      <c r="M48" s="40"/>
-    </row>
-    <row r="49" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="48" spans="9:13" x14ac:dyDescent="0.3">
+      <c r="L48" s="44" t="s">
+        <v>175</v>
+      </c>
+      <c r="M48" s="44"/>
+    </row>
+    <row r="49" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L49" s="30">
         <v>1</v>
       </c>
@@ -2802,7 +2802,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="50" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L50" s="30">
         <v>2</v>
       </c>
@@ -2810,7 +2810,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="51" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L51" s="30">
         <v>3</v>
       </c>
@@ -2818,7 +2818,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="52" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L52" s="30">
         <v>4</v>
       </c>
@@ -2826,7 +2826,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="53" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L53" s="30">
         <v>5</v>
       </c>
@@ -2834,7 +2834,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="54" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L54" s="30">
         <v>6</v>
       </c>
@@ -2842,7 +2842,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="55" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L55" s="30">
         <v>7</v>
       </c>
@@ -2850,7 +2850,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="56" spans="12:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L56" s="30">
         <v>8</v>
       </c>
@@ -2876,7 +2876,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -2884,13 +2884,13 @@
     <col min="4" max="4" width="26" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="9" max="9" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+    <row r="1" spans="1:11" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="39" t="s">
         <v>61</v>
       </c>
       <c r="B1" s="38"/>
@@ -2899,7 +2899,7 @@
       <c r="E1" s="38"/>
       <c r="F1" s="38"/>
     </row>
-    <row r="2" spans="1:11" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="37"/>
       <c r="B2" s="38"/>
       <c r="C2" s="38"/>
@@ -2907,7 +2907,7 @@
       <c r="E2" s="38"/>
       <c r="F2" s="38"/>
     </row>
-    <row r="3" spans="1:11" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
@@ -2927,7 +2927,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="57" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>62</v>
       </c>
@@ -2944,10 +2944,10 @@
         <v>12</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="46.15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>66</v>
       </c>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="F5" s="34"/>
     </row>
-    <row r="6" spans="1:11" ht="46.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>70</v>
       </c>
@@ -2982,10 +2982,10 @@
         <v>12</v>
       </c>
       <c r="F6" s="34" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="46.15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
         <v>74</v>
       </c>
@@ -3002,10 +3002,10 @@
         <v>12</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="46.15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>78</v>
       </c>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="F8" s="34"/>
     </row>
-    <row r="9" spans="1:11" ht="46.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>82</v>
       </c>
@@ -3043,173 +3043,173 @@
         <v>104</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I13" s="44" t="s">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="I13" s="40" t="s">
+        <v>176</v>
+      </c>
+      <c r="J13" s="42"/>
+      <c r="K13" s="35" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="I14" s="40" t="s">
+        <v>173</v>
+      </c>
+      <c r="J14" s="41"/>
+      <c r="K14" s="42"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="I15" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="J13" s="46"/>
-      <c r="K13" s="35" t="s">
+      <c r="J15" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="K15" s="19" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="I16" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="J16" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="K16" s="19" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="17" spans="9:11" x14ac:dyDescent="0.3">
+      <c r="I17" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="J17" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="K17" s="19" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="18" spans="9:11" x14ac:dyDescent="0.3">
+      <c r="I18" s="40" t="s">
+        <v>174</v>
+      </c>
+      <c r="J18" s="41"/>
+      <c r="K18" s="42"/>
+    </row>
+    <row r="19" spans="9:11" x14ac:dyDescent="0.3">
+      <c r="I19" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="J19" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="K19" s="19" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="20" spans="9:11" x14ac:dyDescent="0.3">
+      <c r="I20" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="J20" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="K20" s="19" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="21" spans="9:11" x14ac:dyDescent="0.3">
+      <c r="I21" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="J21" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="K21" s="19" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="22" spans="9:11" x14ac:dyDescent="0.3">
+      <c r="I22" s="40" t="s">
+        <v>175</v>
+      </c>
+      <c r="J22" s="41"/>
+      <c r="K22" s="42"/>
+    </row>
+    <row r="23" spans="9:11" x14ac:dyDescent="0.3">
+      <c r="I23" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="J23" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="K23" s="19" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="24" spans="9:11" x14ac:dyDescent="0.3">
+      <c r="I24" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="J24" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="K24" s="19" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="25" spans="9:11" x14ac:dyDescent="0.3">
+      <c r="I25" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="J25" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="K25" s="19" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="26" spans="9:11" x14ac:dyDescent="0.3">
+      <c r="I26" s="40" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I14" s="44" t="s">
-        <v>174</v>
-      </c>
-      <c r="J14" s="45"/>
-      <c r="K14" s="46"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I15" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="J15" s="19" t="s">
+      <c r="J26" s="41"/>
+      <c r="K26" s="42"/>
+    </row>
+    <row r="27" spans="9:11" x14ac:dyDescent="0.3">
+      <c r="I27" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="J27" s="19" t="s">
         <v>190</v>
       </c>
-      <c r="K15" s="19" t="s">
+      <c r="K27" s="19" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="28" spans="9:11" x14ac:dyDescent="0.3">
+      <c r="I28" s="19" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I16" s="19" t="s">
-        <v>180</v>
-      </c>
-      <c r="J16" s="19" t="s">
+      <c r="J28" s="19" t="s">
         <v>190</v>
       </c>
-      <c r="K16" s="19" t="s">
+      <c r="K28" s="19" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="29" spans="9:11" x14ac:dyDescent="0.3">
+      <c r="I29" s="19" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="17" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I17" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="J17" s="19" t="s">
+      <c r="J29" s="19" t="s">
         <v>190</v>
       </c>
-      <c r="K17" s="19" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="18" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I18" s="44" t="s">
-        <v>175</v>
-      </c>
-      <c r="J18" s="45"/>
-      <c r="K18" s="46"/>
-    </row>
-    <row r="19" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I19" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="J19" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="K19" s="19" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="20" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I20" s="19" t="s">
-        <v>180</v>
-      </c>
-      <c r="J20" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="K20" s="19" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="21" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I21" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="J21" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="K21" s="19" t="s">
+      <c r="K29" s="19" t="s">
         <v>185</v>
-      </c>
-    </row>
-    <row r="22" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I22" s="44" t="s">
-        <v>176</v>
-      </c>
-      <c r="J22" s="45"/>
-      <c r="K22" s="46"/>
-    </row>
-    <row r="23" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I23" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="J23" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="K23" s="19" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="24" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I24" s="19" t="s">
-        <v>180</v>
-      </c>
-      <c r="J24" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="K24" s="19" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="25" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I25" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="J25" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="K25" s="19" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="26" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I26" s="44" t="s">
-        <v>189</v>
-      </c>
-      <c r="J26" s="45"/>
-      <c r="K26" s="46"/>
-    </row>
-    <row r="27" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I27" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="J27" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="K27" s="19" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="28" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I28" s="19" t="s">
-        <v>180</v>
-      </c>
-      <c r="J28" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="K28" s="19" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="29" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I29" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="J29" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="K29" s="19" t="s">
-        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -3230,17 +3230,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="29.7109375" customWidth="1"/>
+    <col min="6" max="6" width="29.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="47" t="s">
         <v>86</v>
       </c>
@@ -3250,7 +3250,7 @@
       <c r="E1" s="38"/>
       <c r="F1" s="38"/>
     </row>
-    <row r="2" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="37" t="s">
         <v>1</v>
       </c>
@@ -3260,7 +3260,7 @@
       <c r="E2" s="38"/>
       <c r="F2" s="38"/>
     </row>
-    <row r="3" spans="1:8" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>2</v>
       </c>
@@ -3280,7 +3280,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="133.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="133.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>87</v>
       </c>
@@ -3297,11 +3297,11 @@
         <v>37</v>
       </c>
       <c r="F4" s="34" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H4" s="20"/>
     </row>
-    <row r="5" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>90</v>
       </c>
@@ -3318,10 +3318,10 @@
         <v>37</v>
       </c>
       <c r="F5" s="36" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="46.15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>94</v>
       </c>
